--- a/data_extactor/batch_10_fa/batch_0041_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0041_fa.xlsx
@@ -503,12 +503,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AceTools.biz Ace Translator | Adapt It | AmoK Translator | Ashkon Translation Pad | Babylon Online Translator | DocTranslate | فرهنگ‌های لغت الکترونیک | ExcelTrans Translator | نرم‌افزار Extensible hypertext markup language XHTML | Google Translate Client | HunterSoft Business Translator | نرم‌افزار Hypertext markup language HTML | Intrado SchoolMessenger | Language Engineering Corporation Translate Pro | Lingoes | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OmegaT | نرم‌افزار بهره‌وری | Smart Link Corporation ImTranslator | Stormdance CatsCradle | نرم‌افزار سیستم Voice over internet protocol VoIP | نرم‌افزار مرورگر وب | jalada GmbH Just Translate</t>
+          <t>AceTools.biz Ace Translator | Adapt It | AmoK Translator | Ashkon Translation Pad | Babylon Online Translator | DocTranslate | فرهنگ‌های لغت الکترونیک | ExcelTrans Translator | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | Google Translate Client | HunterSoft Business Translator | زبان نشانه‌گذاری ابرمتن HTML | Intrado SchoolMessenger | Language Engineering Corporation Translate Pro | Lingoes | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OmegaT | نرم‌افزار بهره‌وری | Smart Link Corporation ImTranslator | Stormdance CatsCradle | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | jalada GmbH Just Translate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب خواندن | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | بیان نوشتاری | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | خلاقیت | روانی ایده‌ها | توجه شنیداری | اشتراک زمانی | سرعت بستن | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | اصالت | روانی ایده‌ها | توجه شنیداری | تقسیم توجه | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | ایمیل | تناوب تصمیم‌گیری | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | فشار زمانی | سطح رقابت | مکالمات تلفنی | صرف زمان برای نشستن | پیامد خطا | مجاورت فیزیکی</t>
+          <t>اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | فشار زمانی | سطح رقابت | مکالمات تلفنی | صرف زمان برای نشستن | پیامد خطا | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان مدرسه ابتدایی، به جز آموزش ویژه | معلمان زبان و ادبیات انگلیسی، پس از متوسطه | بایگان‌ها | معلمان زبان و ادبیات خارجی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | تکنسین‌های کتابخانه | نویسندگان متون پزشکی | معلمان مدرسه راهنمایی، به جز آموزش ویژه و شغلی/فنی | نمونه‌خوان‌ها و علامت‌گذاران کپی | معلمان مدرسه متوسطه، به جز آموزش ویژه و شغلی/فنی | دستیاران پژوهشی علوم اجتماعی | معلمان آموزش ویژه، مدرسه راهنمایی | آسیب‌شناسان گفتار-زبان | دستیاران آسیب‌شناسی گفتار-زبان | نویسندگان فنی | معلمان خصوصی | پردازشگران کلمه و تایپیست‌ها</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | کارمندان بایگانی | مدرسان زبان و ادبیات خارجی، آموزش عالی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | تکنسین‌های کتابخانه | نسخه‌نویسان پزشکی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مصححان و نشانه‌گذاران کپی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | دستیاران تحقیقات علوم اجتماعی | معلمان آموزش ویژه، راهنمایی | آسیب‌شناسان گفتار و زبان | دستیاران آسیب‌شناسی گفتار-زبان | نویسندگان فنی | معلمان خصوصی | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نوشتن | درک مطلب خواندن | نظارت | صحبت کردن</t>
+          <t>گوش دادن فعال | نگارش | درک مطلب | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اداری | کامپیوتر و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | ارتباطات و رسانه</t>
+          <t>زبان انگلیسی | اداری | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | تشخیص گفتار | بیان نوشتاری | درک نوشتاری | بیان شفاهی | دید نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | وضوح گفتار | سرعت مچ-انگشت | مهارت انگشتان</t>
+          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | درک کتبی | بیان شفاهی | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | وضوح گفتار | سرعت مچ و انگشتان | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای نشستن | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های نوشتاری | صرف زمان برای انجام حرکات تکراری | مجاورت فیزیکی</t>
+          <t>اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | کارمندان مکاتبات | کارمندان دادگاه، شهرداری و مجوزها | واردکنندگان داده | متخصصان مدیریت اسناد | منشی‌های اجرایی و دستیاران اداری اجرایی | بایگان‌ها | قضات، قضات دادگاه‌های بدوی و قضات صلح | دستیاران حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | متخصصان سوابق پزشکی | نویسندگان متون پزشکی | کارمندان عمومی دفتر | دستیاران حقوقی و وکلا | نمونه‌خوان‌ها و علامت‌گذاران کپی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری | بررسی‌کنندگان اسناد مالکیت، خلاصه‌نویسان و جستجوگران | پردازشگران کلمه و تایپیست‌ها</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | کارمندان مکاتبات | کارمندان دادگاه، شهرداری و مجوز | اپراتورهای ورود داده | متخصصان مدیریت اسناد | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | متخصصان مدارک پزشکی | نسخه‌نویسان پزشکی | کارمندان دفتری عمومی | پارالیگال‌ها و دستیاران حقوقی | مصححان و نشانه‌گذاران کپی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | فروش و بازاریابی | خدمات مشتری و شخصی | هنرهای زیبا | مدیریت و اداره | آموزش و پرورش</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | خدمات مشتری و شخصی | هنرهای زیبا | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های نوشتاری | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ویراستاران | نویسندگان فنی | نویسندگان و مؤلفان | شاعران، ترانه‌سرایان و نویسندگان خلاق | متخصصان روابط عمومی | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | مترجمان شفاهی و کتبی | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | گویندگان پخش و دی‌جی‌های رادیو | طراحان گرافیک | مدیران هنری | تهیه‌کنندگان و کارگردانان | مدیران برنامه‌ریزی رسانه | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | مدیران روابط عمومی | مدیران بازاریابی | طراحان رابط وب و دیجیتال | عکاسان | تدوینگران فیلم و ویدئو | معلمان ارتباطات، پس از متوسطه</t>
+          <t>ویراستاران | نویسندگان فنی | نویسندگان و مؤلفان | شاعران، ترانه‌سرایان و نویسندگان خلاق | متخصصان روابط عمومی | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | مترجمان شفاهی و کتبی | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | طراحان گرافیک | مدیران هنری | تهیه‌کنندگان و کارگردانان | مدیران برنامه‌ریزی رسانه | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران روابط عمومی | مدیران بازاریابی | طراحان رابط دیجیتال و وب | عکاسان | تدوینگران فیلم و ویدئو | مدرسان ارتباطات، آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe After Effects | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple Final Cut Pro | Apple iMovie | نرم‌افزار Blackboard | Cisco IOS | Cisco Webex | Corel Ulead DVD Workshop | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Windows | Microsoft Word | نرم‌افزار سیستم Voice over internet protocol VoIP | نرم‌افزار مرورگر وب | YouTube | Zoom</t>
+          <t>Adobe After Effects | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple Final Cut Pro | Apple iMovie | نرم‌افزار Blackboard | Cisco IOS | Cisco Webex | Corel Ulead DVD Workshop | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Windows | Microsoft Word | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | YouTube | Zoom</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب خواندن | تفکر انتقادی | صحبت کردن | گوش دادن فعال | نوشتن | یادگیری فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مخابرات | هنرهای زیبا | مهندسی و فناوری | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | مدیریت و اداره</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مخابرات | هنرهای زیبا | مهندسی و فناوری | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | تشخیص رنگ بصری | حساسیت شنوایی | دید دور | دقت کنترل | ثبات دست-بازو | توجه انتخابی | انعطاف‌پذیری بستن | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | مهارت انگشتان | مهارت دستی | اشتراک زمانی | تجسم | سرعت ادراکی</t>
+          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص رنگ بصری | حساسیت شنوایی | بینایی دور | دقت کنترل | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | مهارت انگشتان | مهارت دستی | تقسیم توجه | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | ایمیل | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | اهمیت تکرار وظایف مشابه | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | تناوب تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ایمیل | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های پخش | تکنسین‌ها و متخصصان کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | متخصصان پشتیبانی شبکه کامپیوتری | متخصصان پشتیبانی کاربر کامپیوتر | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تدوینگران فیلم و ویدئو | تکنسین‌های نورپردازی | مدیران برنامه‌ریزی رسانه | مدیران/تکنسین‌های فنی رسانه | متصدیان نمایش فیلم | توزیع‌کنندگان و اعزام‌کنندگان برق | نصاب‌ها و تعمیرکاران رادیو، سلولی و دکل | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به جز نصاب‌های خط</t>
+          <t>نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های پخش | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | متخصصان پشتیبانی شبکه کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تدوینگران فیلم و ویدئو | تکنسین‌های نورپردازی | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | آپاراتچی‌های سینما | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adobe After Effects | Adobe Audition | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Autodesk AutoCAD | نرم‌افزار ویرایش صوتی تصویری Avid Technology | نرم‌افزار تولیدکننده کاراکتر | Cisco IOS | Dassault Systemes CATIA | نرم‌افزار ایمیل | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | UNIX | نرم‌افزار رمزگشای ویدئو | نرم‌افزار رمزگذار ویدئو</t>
+          <t>Adobe After Effects | Adobe Audition | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Autodesk AutoCAD | نرم‌افزار ویرایش صوتی تصویری Avid Technology | نرم‌افزار تولیدکننده شخصیت | Cisco IOS | Dassault Systemes CATIA | نرم‌افزار ایمیل | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | UNIX | نرم‌افزار رمزگشای ویدئو | نرم‌افزار رمزگذار ویدئو</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | نظارت | نوشتن | درک مطلب خواندن | صحبت کردن | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | نگارش | درک مطلب | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مخابرات | مهندسی و فناوری | ارتباطات و رسانه | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مخابرات | مهندسی و فناوری | ارتباطات و رسانه | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک نوشتاری | حساسیت به مسئله | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستن | استدلال استقرایی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست-بازو | تجسم | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها | سرعت ادراکی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | استدلال استقرایی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تجسم | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | تناوب تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی هوافضا و عملیات | تکنسین‌های صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌ها و متخصصان کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و متخصصان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | مدیران/تکنسین‌های فنی رسانه | توزیع‌کنندگان و اعزام‌کنندگان برق | متخصصان دستگاه شناسایی فرکانس رادیویی | نصاب‌ها و تعمیرکاران رادیو، سلولی و دکل | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | متخصصان مهندسی مخابرات | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به جز نصاب‌های خط</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های صوتی و تصویری | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | مدیران/کارگردانان فنی رسانه | توزیع‌کنندگان و دیسپچرهای برق | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Audition | نرم‌افزار Adobe Creative Cloud | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple macOS | نرم‌افزار ویرایش صوتی | Autodesk AutoCAD | Avid Pro Tools | Avid Technology Pro Tools | نرم‌افزار ویرایش صوتی تصویری Avid Technology | Cisco IOS | Facebook | Git | IBM Middleware | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار رابط دیجیتال ساز موسیقی MIDI | Oracle Java | نرم‌افزار Perforce | نرم‌افزار سیستم عامل زمان واقعی RTOS | UNIX | Unity Technologies Unity | VMware | نرم‌افزار سیستم Voice over internet protocol VoIP</t>
+          <t>Adobe Acrobat | Adobe Audition | نرم‌افزار Adobe Creative Cloud | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple macOS | نرم‌افزار ویرایش صوتی | Autodesk AutoCAD | Avid Pro Tools | Avid Technology Pro Tools | نرم‌افزار ویرایش صوتی تصویری Avid Technology | Cisco IOS | Facebook | Git | IBM Middleware | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | Oracle Java | نرم‌افزار Perforce | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | UNIX | Unity Technologies Unity | VMware | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | تفکر انتقادی | درک مطلب خواندن | نوشتن | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتری و شخصی | هنرهای زیبا | زبان انگلیسی | مهندسی و فناوری | ارتباطات و رسانه | تولید و پردازش</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | هنرهای زیبا | زبان انگلیسی | مهندسی و فناوری | ارتباطات و رسانه | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | درک شفاهی | بیان شفاهی | دید نزدیک | توجه شنیداری | توجه انتخابی | روانی ایده‌ها | استدلال قیاسی | خلاقیت | درک نوشتاری | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستن | وضوح گفتار | سرعت بستن | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | دقت کنترل | سرعت ادراکی | تشخیص گفتار | دید دور | مهارت انگشتان | مهارت دستی | ثبات دست-بازو</t>
+          <t>حساسیت شنوایی | درک شفاهی | بیان شفاهی | بینایی نزدیک | توجه شنیداری | توجه انتخابی | روانی ایده‌ها | استدلال قیاسی | اصالت | درک کتبی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | وضوح گفتار | سرعت بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | دقت کنترل | سرعت ادراکی | تشخیص گفتار | بینایی دور | مهارت انگشتان | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | سطح رقابت | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای نشستن | مکالمات تلفنی | آزادی در تصمیم‌گیری | فشار زمانی | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | مجاورت فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | سطح رقابت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای نشستن | مکالمات تلفنی | آزادی در تصمیم‌گیری | فشار زمانی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی هوافضا و عملیات | تکنسین‌های صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های پخش | تکنسین‌ها و متخصصان کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تدوینگران فیلم و ویدئو | تکنسین‌های نورپردازی | مدیران/تکنسین‌های فنی رسانه | متصدیان نمایش فیلم | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تهیه‌کنندگان و کارگردانان | متخصصان دستگاه شناسایی فرکانس رادیویی | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های صوتی و تصویری | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های پخش | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تدوینگران فیلم و ویدئو | تکنسین‌های نورپردازی | مدیران/کارگردانان فنی رسانه | آپاراتچی‌های سینما | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تهیه‌کنندگان و کارگردانان | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | FileMaker Pro | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | Rockwell RSLogix | SAP Maintenance</t>
+          <t>Autodesk AutoCAD | FileMaker Pro | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Rockwell RSLogix | SAP Maintenance</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | تفکر انتقادی | نظارت | گوش دادن فعال | صحبت کردن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | هنرهای زیبا | مهندسی و فناوری | زبان انگلیسی | ارتباطات و رسانه | طراحی | ایمنی و امنیت عمومی | مکانیکی</t>
+          <t>رایانه و الکترونیک | هنرهای زیبا | مهندسی و فناوری | زبان انگلیسی | ارتباطات و رسانه | طراحی | ایمنی و امنیت عمومی | مکانیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دید نزدیک | تجسم | ثبات دست-بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندامی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور | تشخیص رنگ بصری | زمان واکنش</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | تشخیص رنگ بصری | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | صرف زمان برای ایستادن | محیط داخلی، دارای کنترل محیطی نیست | صرف زمان برای بالا رفتن از نردبان، داربست یا ستون | قرار گرفتن در مکان‌های مرتفع | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | فشار زمانی | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | مجاورت فیزیکی | آزادی در تصمیم‌گیری | ایمیل | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | فشار زمانی | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | ایمیل | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، دکل‌بندی و سیستم‌های هواپیما | تکنسین‌های اویونیک | نصاب‌ها و تعمیرکاران کنترل و شیر، به جز درب مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و مرتبط | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تعمیرکاران برق و الکترونیک، نیروگاه، پست و رله | برقکاران | مونتاژکنندگان تجهیزات الکترومکانیکی | نصاب‌ها و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | کمک‌برقکاران | کارگران نگهداری و تعمیرات، عمومی | کارگران کارخانه | لوله‌کش‌ها، نصاب‌های لوله و بخار | توزیع‌کنندگان و اعزام‌کنندگان برق | تکنسین‌های رباتیک | نصاب‌های سیستم‌های هشدار امنیتی و آتش‌سوزی | نصاب‌های فتوولتائیک خورشیدی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های هوانوردی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | دستیاران--برق‌کاران | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | نصابان سیستم‌های فتوولتائیک خورشیدی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب خواندن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | فروش و بازاریابی | کامپیوتر و الکترونیک | مدیریت و اداره | ارتباطات و رسانه | زبان انگلیسی | هنرهای زیبا | تولید و پردازش | اداری | روانشناسی | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | ارتباطات و رسانه | زبان انگلیسی | هنرهای زیبا | تولید و فرآوری | اداری | روان‌شناسی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | خلاقیت | تجسم | دید دور | تشخیص رنگ بصری | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک نوشتاری | روانی ایده‌ها | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | مهارت دستی | ثبات دست-بازو | توجه انتخابی | انعطاف‌پذیری بستن | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان نوشتاری</t>
+          <t>بینایی نزدیک | بیان شفاهی | اصالت | تجسم | بینایی دور | تشخیص رنگ بصری | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | روانی ایده‌ها | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم | سطح رقابت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | مجاورت فیزیکی | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | تناوب تصمیم‌گیری</t>
+          <t>ایمیل | مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران هنری | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | هنرمندان صنایع دستی | ناشران رومیزی | حکاکان و قلم‌زنان | تدوینگران فیلم و ویدئو | هنرمندان زیبا، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل | طراحان گرافیک | آرایشگران، تئاتری و اجرایی | نمایش‌دهندگان کالا و تزئین‌کنندگان ویترین | متصدیان نمایش فیلم | کارگران فرآیند عکاسی و اپراتورهای ماشین پردازش | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | هنرمندان و انیماتورهای جلوه‌های ویژه | نویسندگان فنی | نویسندگان و مؤلفان</t>
+          <t>مدیران هنری | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | هنرمندان صنایع دستی | ناشران رومیزی | حکاکان و تیزاب‌کاران | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل | طراحان گرافیک | میکاپ آرتیست‌های تئاتر و نمایش | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | آپاراتچی‌های سینما | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | نویسندگان فنی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple Final Cut Studio | نرم‌افزار ویرایش صوتی تصویری Avid Technology | DaVinci Resolve | نرم‌افزار ایمیل | Google Drive | Litchi | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Pix4D Pix4Dcapture | TikTok | نرم‌افزار ویرایش ویدئو | YouTube</t>
+          <t>Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple Final Cut Studio | نرم‌افزار ویرایش صوتی تصویری Avid Technology | DaVinci Resolve | نرم‌افزار ایمیل | Google Drive | Litchi | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Pix4D Pix4Dcapture | TikTok | نرم‌افزار ویرایش ویدیو | YouTube</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب خواندن | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | کامپیوتر و الکترونیک | ارتباطات و رسانه | مخابرات</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | مخابرات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم | دید نزدیک | دید دور | بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستن | توجه انتخابی | ثبات دست-بازو | دقت کنترل | استدلال قیاسی | خلاقیت | روانی ایده‌ها | استدلال استقرایی | مهارت انگشتان | مهارت دستی | اشتراک زمانی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>تجسم | بینایی نزدیک | بینایی دور | بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | دقت کنترل | استدلال قیاسی | اصالت | روانی ایده‌ها | استدلال استقرایی | مهارت انگشتان | مهارت دستی | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | فشار زمانی | مکالمات تلفنی | مجاورت فیزیکی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | مکالمات تلفنی | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی هوافضا و عملیات | مونتاژکنندگان سازه، سطوح، دکل‌بندی و سیستم‌های هواپیما | تکنسین‌های صوتی و تصویری | تکنسین‌های اویونیک | تکنسین‌های پخش | تکنسین‌ها و متخصصان کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و متخصصان الکترومکانیک و مکاترونیک | تدوینگران فیلم و ویدئو | تکنسین‌های نورپردازی | مدیران/تکنسین‌های فنی رسانه | متصدیان نمایش فیلم | تهیه‌کنندگان و کارگردانان | نصاب‌ها و تعمیرکاران رادیو، سلولی و دکل | دانشمندان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های صوتی و تصویری | تکنسین‌های هوانوردی | تکنسین‌های پخش | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | تدوینگران فیلم و ویدئو | تکنسین‌های نورپردازی | مدیران/کارگردانان فنی رسانه | آپاراتچی‌های سینما | تهیه‌کنندگان و کارگردانان | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AJAX | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple DVD Studio Pro | Apple Final Cut Pro | Apple QuickTime | Apple Xsan | Autodesk Maya | Autodesk Smoke | Avid Digidesign Pro Tools | نرم‌افزار ویرایش صوتی تصویری Avid Technology | Boris FX Continuum Complete | Brightcove | Cascading style sheets CSS | DaVinci Resolve | نرم‌افزار Extensible markup language XML | Google Video | نرم‌افزار Hypertext markup language HTML | Instagram | JavaScript | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | RSS | Screencastify | Sorenson Media Sorenson Squeeze | TikTok | نرم‌افزار ویرایش ویدئو | نرم‌افزار مرورگر وب | Windows Media Services | YouTube</t>
+          <t>AJAX | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple DVD Studio Pro | Apple Final Cut Pro | Apple QuickTime | Apple Xsan | Autodesk Maya | Autodesk Smoke | Avid Digidesign Pro Tools | نرم‌افزار ویرایش صوتی تصویری Avid Technology | Boris FX Continuum Complete | Brightcove | برگه‌های سبک آبشاری CSS | DaVinci Resolve | زبان نشانه‌گذاری توسعه‌پذیر XML | Google Video | زبان نشانه‌گذاری ابرمتن HTML | Instagram | JavaScript | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | RSS | Screencastify | Sorenson Media Sorenson Squeeze | TikTok | نرم‌افزار ویرایش ویدیو | نرم‌افزار مرورگر وب | Windows Media Services | YouTube</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | یادگیری فعال | صحبت کردن | نوشتن | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | مخابرات | هنرهای زیبا | تولید و پردازش | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره | طراحی | اداری | فروش و بازاریابی | آموزش و پرورش</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | مخابرات | هنرهای زیبا | تولید و فرآوری | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره | طراحی | اداری | فروش و بازاریابی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | تجسم | روانی ایده‌ها | درک نوشتاری | خلاقیت | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان نوشتاری | حساسیت به مسئله | تشخیص رنگ بصری | سرعت ادراکی | انعطاف‌پذیری بستن | استدلال استقرایی</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | تجسم | روانی ایده‌ها | درک کتبی | اصالت | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | تشخیص رنگ بصری | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | فشار زمانی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | تماس با دیگران | آزادی در تصمیم‌گیری | سطح رقابت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | سطح رقابت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های صوتی و تصویری | گویندگان پخش و دی‌جی‌های رادیو | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | ناشران رومیزی | ویراستاران | طراحان گرافیک | مدیران برنامه‌ریزی رسانه | مدیران/تکنسین‌های فنی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | عکاسان | کارگران فرآیند عکاسی و اپراتورهای ماشین پردازش | شاعران، ترانه‌سرایان و نویسندگان خلاق | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | نمونه‌خوان‌ها و علامت‌گذاران کپی | تکنسین‌های مهندسی صدا | هنرمندان و انیماتورهای جلوه‌های ویژه | نویسندگان فنی | طراحان بازی ویدئویی | نویسندگان و مؤلفان</t>
+          <t>تکنسین‌های صوتی و تصویری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | ناشران رومیزی | ویراستاران | طراحان گرافیک | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | عکاسان | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | شاعران، ترانه‌سرایان و نویسندگان خلاق | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | مصححان و نشانه‌گذاران کپی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | نویسندگان فنی | طراحان بازی‌های ویدئویی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0041_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0041_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | زبان‌های خارجی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | امور اداری و دفتری | ایمنی و امنیت عمومی | حقوق و امور دولتی</t>
+          <t>زبان انگلیسی | زبان خارجی | خدمات مشتری و شخصی | آموزش و پرورش | اداری | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | ابتکار | روانی ایده‌ها | توجه شنیداری | تقسیم توجه | سرعت درک نهایی | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | اصالت | روانی ایده‌ها | توجه شنیداری | تقسیم توجه | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به عنوان زبان دوم | معلمان دوره ابتدایی، به جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | کارمندان بایگانی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | هماهنگ‌کنندگان برنامه‌های آموزشی | کارشناسان کتابداری و مجموعه‌های رسانه‌ای | دستیاران دفتری کتابخانه | کاردان‌های فنی کتابداری | پیاده‌سازان متون پزشکی | معلمان دوره اول متوسطه، به جز آموزش استثنایی و فنی‌وحرفه‌ای | نمونه‌خوانان و تصحیح‌کنندگان متون چاپی | معلمان دوره دوم متوسطه، به جز آموزش استثنایی و فنی‌وحرفه‌ای | کارشناسان پژوهشی علوم اجتماعی | معلمان آموزش استثنایی دوره اول متوسطه | گفتاردرمانگران | دستیاران گفتاردرمانی | نویسندگان متون فنی و تخصصی | معلمان خصوصی و مدرسان کمکی | تایپیست‌ها و متصدیان پردازش متن</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | متصدیان بایگانی و اسناد | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | تکنسین‌های کتابداری | پیاده‌سازان و تایپیست‌های متون پزشکی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | ویراستاران فنی و نمونه‌خوان‌ها | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | معلمان آموزش استثنایی دوره اول متوسطه | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی) | نویسندگان متون فنی | معلمان خصوصی و مدرسان تقویتی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | درک مطلب | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | نگارش | درک مطلب | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امور اداری و دفتری | کامپیوتر و الکترونیک | حقوق و امور دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>زبان انگلیسی | اداری | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | درک کتبی | بیان شفاهی | دید نزدیک | توجه انتخابی | مرتب‌سازی اطلاعات | وضوح گفتار | سرعت مچ و انگشتان | چابکی انگشتان</t>
+          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | درک کتبی | بیان شفاهی | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | وضوح گفتار | سرعت مچ و انگشتان | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، دادرسان و مسئولان استماع | کارمندان امور مکاتبات | کارمندان دادگاه، شهرداری و صدور پروانه | متصدیان ورود اطلاعات | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی | قضات، دادرسان ارشد و مستشاران قضایی | داد‌یاران و کارشناسان حقوقی قضایی | وکلا | مسئولان دفاتر و دستیاران امور حقوقی | کارشناسان مدارک پزشکی | پیاده‌سازان متون پزشکی | کارمندان عمومی امور دفتری | کارشناسان امور حقوقی و دستیاران وکالت | نمونه‌خوانان و تصحیح‌کنندگان متون چاپی | مسئولان دفاتر و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | کارشناسان آمار | کارشناسان بررسی و جستجوی اسناد ثبتی | تایپیست‌ها و متصدیان پردازش متن</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | پیاده‌سازان و تایپیست‌های متون پزشکی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان و دستیاران امور حقوقی | ویراستاران فنی و نمونه‌خوان‌ها | منشی‌ها و دستیاران اداری عمومی | دستیاران و تکنسین‌های آمار | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | فروش و بازاریابی | خدمات مشتریان و خدمات فردی | هنرهای تجسمی | مدیریت و امور اداری | آموزش و پرورش</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | خدمات مشتری و شخصی | هنرهای زیبا | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | ابتکار | توجه انتخابی | تقسیم توجه | تجسم فضایی | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ویراستاران | نویسندگان متون فنی و تخصصی | نویسندگان و پدیدآورندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | کارشناسان روابط عمومی | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | مترجمان کتبی و شفاهی | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | گویندگان پخش و مجریان برنامه‌های رادیویی | طراحان گرافیک | مدیران هنری | تهیه‌کنندگان و کارگردانان | مدیران برنامه‌ریزی رسانه‌ای | کارشناسان تحقیقات بازار و بازاریابی | مدیران روابط عمومی | مدیران بازاریابی | طراحان صفحات وب و رابط‌های کاربری دیجیتال | عکاسان | تدوین‌گران فیلم و ویدیو | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی</t>
+          <t>ویراستاران | نویسندگان متون فنی | نویسندگان و پدیدآورندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | کارشناسان روابط عمومی | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | مترجمان کتبی و شفاهی | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | گویندگان پخش و مجریان رادیویی | طراحان گرافیک | مدیران هنری | تهیه‌کنندگان و کارگردانان | مدیران برنامه‌ریزی و پخش رسانه | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران روابط عمومی | مدیران بازاریابی | طراحان وب و رابط‌های دیجیتال | عکاسان | تدوین‌گران فیلم و ویدیو | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نگارش | یادگیری فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مخابرات | هنرهای تجسمی | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | آموزش و پرورش | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مخابرات | هنرهای زیبا | مهندسی و فناوری | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص رنگ | حساسیت شنوایی | دید دور | دقت کنترل | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری در بستن الگو | انعطاف‌پذیری در دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | چابکی انگشتان | چابکی دستی | تقسیم توجه | تجسم فضایی | سرعت ادراک</t>
+          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص رنگ بصری | حساسیت شنوایی | بینایی دور | دقت کنترل | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | مهارت انگشتان | مهارت دستی | تقسیم توجه | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نصاب‌ها و تعمیرکاران تجهیزات سمعی و بصری | تکنسین‌های پخش | تکنسین‌ها و کاردان‌های فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | کارشناسان پشتیبانی شبکه‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | مدیران برنامه‌ریزی رسانه‌ای | مدیران فنی رسانه | آپاراتچی‌ها و متصدیان نمایش فیلم | توزیع‌کنندگان و دیسپچرهای برق | نصاب‌ها و تعمیرکاران دکل‌ها و تجهیزات رادیویی و سلولی | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به جز خطوط ارتباطی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | متخصصان پشتیبانی شبکه رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | دیسپچرها و توزیع‌کنندگان شبکه برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | نگارش | درک مطلب | سخن گفتن | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | نگارش | درک مطلب | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مخابرات | مهندسی و فناوری | ارتباطات و رسانه | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مخابرات | مهندسی و فناوری | ارتباطات و رسانه | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستن الگو | استدلال استقرایی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ | دقت کنترل | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | تجسم فضایی | انعطاف‌پذیری در دسته‌بندی | ابتکار | روانی ایده‌ها | سرعت ادراک</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | استدلال استقرایی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تجسم | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی مهندسی هوافضا و عملیات پرواز | تکنسین‌های تجهیزات صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات سمعی و بصری | تکنسین‌ها و کاردان‌های فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | معماران شبکه‌های کامپیوتری | کارشناسان پشتیبانی شبکه‌های کامپیوتری | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کاردان‌های فنی الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | مدیران فنی رسانه | توزیع‌کنندگان و دیسپچرهای برق | کارشناسان سیستم‌های شناسایی با امواج رادیویی (RFID) | نصاب‌ها و تعمیرکاران دکل‌ها و تجهیزات رادیویی و سلولی | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | کارشناسان مهندسی مخابرات | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به جز خطوط ارتباطی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌های نورپردازی | مدیران فنی رسانه | دیسپچرها و توزیع‌کنندگان شبکه برق | متخصصان سامانه‌های شناسایی با امواج رادیویی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتریان و خدمات فردی | هنرهای تجسمی | زبان انگلیسی | مهندسی و فناوری | ارتباطات و رسانه | تولید و فرآوری</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | هنرهای زیبا | زبان انگلیسی | مهندسی و فناوری | ارتباطات و رسانه | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | درک شفاهی | بیان شفاهی | دید نزدیک | توجه شنیداری | توجه انتخابی | روانی ایده‌ها | استدلال قیاسی | ابتکار | درک کتبی | بیان کتبی | انعطاف‌پذیری در دسته‌بندی | انعطاف‌پذیری در بستن الگو | وضوح گفتار | سرعت درک نهایی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | دقت کنترل | سرعت ادراک | تشخیص گفتار | دید دور | چابکی انگشتان | چابکی دستی | ثبات دست و بازو</t>
+          <t>حساسیت شنوایی | درک شفاهی | بیان شفاهی | بینایی نزدیک | توجه شنیداری | توجه انتخابی | روانی ایده‌ها | استدلال قیاسی | اصالت | درک کتبی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | وضوح گفتار | سرعت بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | دقت کنترل | سرعت ادراکی | تشخیص گفتار | بینایی دور | مهارت انگشتان | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی مهندسی هوافضا و عملیات پرواز | تکنسین‌های تجهیزات صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات سمعی و بصری | تکنسین‌های پخش | تکنسین‌ها و کاردان‌های فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | برنامه‌نویسان ماشین‌های کنترل عددی رایانه‌ای (CNC) | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | مدیران فنی رسانه | آپاراتچی‌ها و متصدیان نمایش فیلم | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تهیه‌کنندگان و کارگردانان | کارشناسان سیستم‌های شناسایی با امواج رادیویی (RFID) | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | مدیران فنی رسانه | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تهیه‌کنندگان و کارگردانان | متخصصان سامانه‌های شناسایی با امواج رادیویی | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | هنرهای تجسمی | مهندسی و فناوری | زبان انگلیسی | ارتباطات و رسانه | طراحی | ایمنی و امنیت عمومی | مکانیک</t>
+          <t>رایانه و الکترونیک | هنرهای زیبا | مهندسی و فناوری | زبان انگلیسی | ارتباطات و رسانه | طراحی | ایمنی و امنیت عمومی | مکانیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی | دید دور | تشخیص رنگ | زمان واکنش</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | تشخیص رنگ بصری | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | نصاب‌ها و تعمیرکاران شیرآلات و سیستم‌های کنترلی، به جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب‌ها و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | نصاب‌ها و تعمیرکاران تجهیزات الکترونیکی خودرو | کارگران کمکی برق‌کاران | کارگران عمومی تعمیرات و نگهداری | نصاب‌ها و مکانیک‌های صنعتی (میلرایت‌ها) | لوله‌کش‌ها و نصاب‌های خطوط لوله و اتصالات بخار | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | نصاب‌های سیستم‌های امنیتی و اعلام حریق | نصاب‌های پنل‌های خورشیدی فتوولتائیک</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | کمک‌برق‌کاران | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | دیسپچرها و توزیع‌کنندگان شبکه برق | تکنسین‌های رباتیک | نصاب سیستم‌های اعلام سرقت و حریق | نصابان سیستم‌های خورشیدی فتوولتائیک</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | کامپیوتر و الکترونیک | مدیریت و امور اداری | ارتباطات و رسانه | زبان انگلیسی | هنرهای تجسمی | تولید و فرآوری | امور اداری و دفتری | روان‌شناسی | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | ارتباطات و رسانه | زبان انگلیسی | هنرهای زیبا | تولید و فرآوری | اداری | روان‌شناسی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | ابتکار | تجسم فضایی | دید دور | تشخیص رنگ | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | روانی ایده‌ها | استدلال قیاسی | انعطاف‌پذیری در دسته‌بندی | تشخیص گفتار | چابکی دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری در بستن الگو | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان کتبی</t>
+          <t>بینایی نزدیک | بیان شفاهی | اصالت | تجسم | بینایی دور | تشخیص رنگ بصری | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | روانی ایده‌ها | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | هنرمندان صنایع دستی | متخصصان نشر رومیزی | قلم‌زنان و حکاکان | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل و گیاه‌آرایی | طراحان گرافیک | چهره‌پردازان و گریمورهای تئاتر و نمایش | چیدمان‌کنندگان کالا و طراحان ویترین | آپاراتچی‌ها و متصدیان نمایش فیلم | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های چاپ عکس | کاردان‌های فنی و کارگران پیش‌چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و پویانماها | نویسندگان متون فنی و تخصصی | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | هنرمندان صنایع دستی | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | حکاکان و اسیدکاران | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل و گل‌آراها | طراحان گرافیک | چهره‌پردازان و گریموران تئاتر و سینما | طراحان دکوراسیون و ویترین مغازه | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | پویانماها و طراحان جلوه‌های ویژه | نویسندگان متون فنی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | کامپیوتر و الکترونیک | ارتباطات و رسانه | مخابرات</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | مخابرات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | دید دور | بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستن الگو | توجه انتخابی | ثبات دست و بازو | دقت کنترل | استدلال قیاسی | ابتکار | روانی ایده‌ها | استدلال استقرایی | چابکی انگشتان | چابکی دستی | تقسیم توجه | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>تجسم | بینایی نزدیک | بینایی دور | بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | دقت کنترل | استدلال قیاسی | اصالت | روانی ایده‌ها | استدلال استقرایی | مهارت انگشتان | مهارت دستی | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی مهندسی هوافضا و عملیات پرواز | مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک هوانوردی | تکنسین‌های پخش | تکنسین‌ها و کاردان‌های فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کاردان‌های فنی الکترومکانیک و مکاترونیک | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | مدیران فنی رسانه | آپاراتچی‌ها و متصدیان نمایش فیلم | تهیه‌کنندگان و کارگردانان | نصاب‌ها و تعمیرکاران دکل‌ها و تجهیزات رادیویی و سلولی | دانشمندان و متخصصان سنجش از دور | کاردان‌های فنی و تکنسین‌های سنجش از دور | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌های پخش و اتاق فرمان | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | مدیران فنی رسانه | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | تهیه‌کنندگان و کارگردانان | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های رباتیک | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | مخابرات | هنرهای تجسمی | تولید و فرآوری | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | مدیریت و امور اداری | طراحی | امور اداری و دفتری | فروش و بازاریابی | آموزش و پرورش</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | مخابرات | هنرهای زیبا | تولید و فرآوری | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره | طراحی | اداری | فروش و بازاریابی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | مرتب‌سازی اطلاعات | تجسم فضایی | روانی ایده‌ها | درک کتبی | ابتکار | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | تشخیص رنگ | سرعت ادراک | انعطاف‌پذیری در بستن الگو | استدلال استقرایی</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | تجسم | روانی ایده‌ها | درک کتبی | اصالت | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | تشخیص رنگ بصری | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های تجهیزات صوتی و تصویری | گویندگان پخش و مجریان برنامه‌های رادیویی | تصویربرداران تلویزیون، ویدیو و سینما | متخصصان نشر رومیزی | ویراستاران | طراحان گرافیک | مدیران برنامه‌ریزی رسانه‌ای | مدیران فنی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | عکاسان | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های چاپ عکس | شاعران، ترانه‌سرایان و نویسندگان خلاق | کاردان‌های فنی و کارگران پیش‌چاپ | تهیه‌کنندگان و کارگردانان | نمونه‌خوانان و تصحیح‌کنندگان متون چاپی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و پویانماها | نویسندگان متون فنی و تخصصی | طراحان بازی‌های ویدیویی | نویسندگان و پدیدآورندگان</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | گویندگان پخش و مجریان رادیویی | تصویربرداران تلویزیون، ویدیو و سینما | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | ویراستاران | طراحان گرافیک | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | عکاسان | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | شاعران، ترانه‌سرایان و نویسندگان خلاق | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | تهیه‌کنندگان و کارگردانان | ویراستاران فنی و نمونه‌خوان‌ها | تکنسین‌های مهندسی صدا | پویانماها و طراحان جلوه‌های ویژه | نویسندگان متون فنی | طراحان بازی‌های ویدیویی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
